--- a/data/raw/inventory/Week 30/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -907,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
         <v>18</v>
@@ -2445,7 +2445,7 @@
         <v>92</v>
       </c>
       <c r="F33" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
         <v>105</v>

--- a/data/raw/inventory/Week 30/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -706,25 +706,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>15</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>16</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
         <v>32</v>
       </c>
       <c r="G14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -1515,7 +1515,7 @@
         <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>90</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F26" t="n">
         <v>23</v>
@@ -2023,13 +2023,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
         <v>18</v>
@@ -2135,7 +2135,7 @@
         <v>83</v>
       </c>
       <c r="F28" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>93</v>
@@ -2212,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F33" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
@@ -2693,7 +2693,7 @@
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>18</v>

--- a/data/raw/inventory/Week 30/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -957,7 +957,7 @@
         <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>29</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1639,7 +1639,7 @@
         <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
         <v>91</v>
@@ -2150,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
         <v>5</v>
@@ -2708,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -3186,13 +3186,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H45" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L45" t="n">
         <v>4</v>
